--- a/data_u1/rob_secondary_2025.08.15.xlsx
+++ b/data_u1/rob_secondary_2025.08.15.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sksiafis/Documents/GitHub/LSR3_taar1_H/data_u1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D87E9F6-ADB5-8B4E-B045-63DECD8571FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C6A8DA4-7BBD-994D-9911-10B629A0B74D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{5B321493-8628-1E4C-935B-6CFC743B201E}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16300" xr2:uid="{5B321493-8628-1E4C-935B-6CFC743B201E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="9" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1802" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1811" uniqueCount="60">
   <si>
     <t>D1</t>
   </si>
@@ -361,7 +361,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -443,6 +443,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -765,7 +768,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{572FBEC7-01CF-B040-AE68-30BAA13155EF}">
-  <dimension ref="A1:J197"/>
+  <dimension ref="A1:J198"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="28.1640625" customWidth="1"/>
@@ -5389,29 +5392,29 @@
       <c r="A154" s="23" t="s">
         <v>44</v>
       </c>
-      <c r="B154" s="23" t="s">
-        <v>35</v>
+      <c r="B154" s="37" t="s">
+        <v>57</v>
       </c>
       <c r="C154" s="25" t="s">
         <v>23</v>
       </c>
-      <c r="D154" s="35" t="s">
-        <v>5</v>
-      </c>
-      <c r="E154" s="23" t="s">
+      <c r="D154" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="E154" s="25" t="s">
         <v>5</v>
       </c>
       <c r="F154" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="G154" s="23" t="s">
-        <v>5</v>
-      </c>
-      <c r="H154" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="I154" s="23"/>
-      <c r="J154" s="23" t="s">
+      <c r="G154" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="H154" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="I154" s="25"/>
+      <c r="J154" s="25" t="s">
         <v>5</v>
       </c>
     </row>
@@ -5420,12 +5423,12 @@
         <v>44</v>
       </c>
       <c r="B155" s="23" t="s">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="C155" s="25" t="s">
         <v>23</v>
       </c>
-      <c r="D155" s="23" t="s">
+      <c r="D155" s="35" t="s">
         <v>5</v>
       </c>
       <c r="E155" s="23" t="s">
@@ -5449,38 +5452,38 @@
       <c r="A156" s="23" t="s">
         <v>44</v>
       </c>
-      <c r="B156" s="25" t="s">
-        <v>28</v>
+      <c r="B156" s="23" t="s">
+        <v>21</v>
       </c>
       <c r="C156" s="25" t="s">
         <v>23</v>
       </c>
-      <c r="D156" s="25" t="s">
-        <v>5</v>
-      </c>
-      <c r="E156" s="25" t="s">
-        <v>5</v>
-      </c>
-      <c r="F156" s="25" t="s">
-        <v>6</v>
-      </c>
-      <c r="G156" s="25" t="s">
-        <v>5</v>
-      </c>
-      <c r="H156" s="25" t="s">
-        <v>5</v>
-      </c>
-      <c r="I156" s="25"/>
-      <c r="J156" s="25" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="157" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="D156" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="E156" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="F156" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="G156" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="H156" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="I156" s="23"/>
+      <c r="J156" s="23" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="157" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A157" s="23" t="s">
         <v>44</v>
       </c>
       <c r="B157" s="25" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="C157" s="25" t="s">
         <v>23</v>
@@ -5492,7 +5495,7 @@
         <v>5</v>
       </c>
       <c r="F157" s="25" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G157" s="25" t="s">
         <v>5</v>
@@ -5510,7 +5513,7 @@
         <v>44</v>
       </c>
       <c r="B158" s="25" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="C158" s="25" t="s">
         <v>23</v>
@@ -5535,33 +5538,33 @@
         <v>5</v>
       </c>
     </row>
-    <row r="159" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:10" ht="17" x14ac:dyDescent="0.2">
       <c r="A159" s="23" t="s">
         <v>44</v>
       </c>
-      <c r="B159" s="29" t="s">
-        <v>37</v>
+      <c r="B159" s="25" t="s">
+        <v>13</v>
       </c>
       <c r="C159" s="25" t="s">
         <v>23</v>
       </c>
-      <c r="D159" s="23" t="s">
-        <v>5</v>
-      </c>
-      <c r="E159" s="23" t="s">
-        <v>5</v>
-      </c>
-      <c r="F159" s="23" t="s">
-        <v>6</v>
-      </c>
-      <c r="G159" s="23" t="s">
-        <v>5</v>
-      </c>
-      <c r="H159" s="23" t="s">
-        <v>5</v>
-      </c>
-      <c r="I159" s="23"/>
-      <c r="J159" s="23" t="s">
+      <c r="D159" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="E159" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="F159" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="G159" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="H159" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="I159" s="25"/>
+      <c r="J159" s="25" t="s">
         <v>5</v>
       </c>
     </row>
@@ -5569,8 +5572,8 @@
       <c r="A160" s="23" t="s">
         <v>44</v>
       </c>
-      <c r="B160" s="23" t="s">
-        <v>38</v>
+      <c r="B160" s="29" t="s">
+        <v>37</v>
       </c>
       <c r="C160" s="25" t="s">
         <v>23</v>
@@ -5600,7 +5603,7 @@
         <v>44</v>
       </c>
       <c r="B161" s="23" t="s">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C161" s="25" t="s">
         <v>23</v>
@@ -5629,29 +5632,29 @@
       <c r="A162" s="23" t="s">
         <v>44</v>
       </c>
-      <c r="B162" s="25" t="s">
-        <v>27</v>
+      <c r="B162" s="23" t="s">
+        <v>16</v>
       </c>
       <c r="C162" s="25" t="s">
         <v>23</v>
       </c>
-      <c r="D162" s="25" t="s">
-        <v>5</v>
-      </c>
-      <c r="E162" s="25" t="s">
-        <v>5</v>
-      </c>
-      <c r="F162" s="25" t="s">
-        <v>6</v>
-      </c>
-      <c r="G162" s="25" t="s">
-        <v>5</v>
-      </c>
-      <c r="H162" s="25" t="s">
-        <v>5</v>
-      </c>
-      <c r="I162" s="25"/>
-      <c r="J162" s="25" t="s">
+      <c r="D162" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="E162" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="F162" s="23" t="s">
+        <v>6</v>
+      </c>
+      <c r="G162" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="H162" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="I162" s="23"/>
+      <c r="J162" s="23" t="s">
         <v>5</v>
       </c>
     </row>
@@ -5659,29 +5662,29 @@
       <c r="A163" s="23" t="s">
         <v>44</v>
       </c>
-      <c r="B163" s="31" t="s">
-        <v>49</v>
+      <c r="B163" s="25" t="s">
+        <v>27</v>
       </c>
       <c r="C163" s="25" t="s">
         <v>23</v>
       </c>
-      <c r="D163" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="E163" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="F163" s="23" t="s">
-        <v>6</v>
-      </c>
-      <c r="G163" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="H163" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="I163" s="9"/>
-      <c r="J163" s="9" t="s">
+      <c r="D163" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="E163" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="F163" s="25" t="s">
+        <v>6</v>
+      </c>
+      <c r="G163" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="H163" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="I163" s="25"/>
+      <c r="J163" s="25" t="s">
         <v>5</v>
       </c>
     </row>
@@ -5689,29 +5692,29 @@
       <c r="A164" s="23" t="s">
         <v>44</v>
       </c>
-      <c r="B164" s="23" t="s">
-        <v>24</v>
+      <c r="B164" s="31" t="s">
+        <v>49</v>
       </c>
       <c r="C164" s="25" t="s">
         <v>23</v>
       </c>
-      <c r="D164" s="23" t="s">
-        <v>5</v>
-      </c>
-      <c r="E164" s="23" t="s">
+      <c r="D164" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="E164" s="9" t="s">
         <v>5</v>
       </c>
       <c r="F164" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="G164" s="23" t="s">
-        <v>5</v>
-      </c>
-      <c r="H164" s="23" t="s">
-        <v>5</v>
-      </c>
-      <c r="I164" s="23"/>
-      <c r="J164" s="23" t="s">
+      <c r="G164" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="H164" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="I164" s="9"/>
+      <c r="J164" s="9" t="s">
         <v>5</v>
       </c>
     </row>
@@ -5720,7 +5723,7 @@
         <v>44</v>
       </c>
       <c r="B165" s="23" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C165" s="25" t="s">
         <v>23</v>
@@ -5749,29 +5752,29 @@
       <c r="A166" s="23" t="s">
         <v>44</v>
       </c>
-      <c r="B166" s="25" t="s">
-        <v>14</v>
+      <c r="B166" s="23" t="s">
+        <v>29</v>
       </c>
       <c r="C166" s="25" t="s">
         <v>23</v>
       </c>
-      <c r="D166" s="25" t="s">
-        <v>5</v>
-      </c>
-      <c r="E166" s="25" t="s">
+      <c r="D166" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="E166" s="23" t="s">
         <v>5</v>
       </c>
       <c r="F166" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="G166" s="25" t="s">
-        <v>5</v>
-      </c>
-      <c r="H166" s="25" t="s">
-        <v>5</v>
-      </c>
-      <c r="I166" s="25"/>
-      <c r="J166" s="25" t="s">
+      <c r="G166" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="H166" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="I166" s="23"/>
+      <c r="J166" s="23" t="s">
         <v>5</v>
       </c>
     </row>
@@ -5780,7 +5783,7 @@
         <v>44</v>
       </c>
       <c r="B167" s="25" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="C167" s="25" t="s">
         <v>23</v>
@@ -5805,36 +5808,34 @@
         <v>5</v>
       </c>
     </row>
-    <row r="168" spans="1:10" ht="17" x14ac:dyDescent="0.2">
-      <c r="A168" s="15" t="s">
-        <v>55</v>
-      </c>
-      <c r="B168" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="C168" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="D168" s="14" t="s">
-        <v>5</v>
-      </c>
-      <c r="E168" s="14" t="s">
-        <v>6</v>
-      </c>
-      <c r="F168" s="14" t="s">
-        <v>5</v>
-      </c>
-      <c r="G168" s="14" t="s">
-        <v>6</v>
-      </c>
-      <c r="H168" s="14" t="s">
-        <v>5</v>
-      </c>
-      <c r="I168" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="J168" s="16" t="s">
-        <v>6</v>
+    <row r="168" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="A168" s="23" t="s">
+        <v>44</v>
+      </c>
+      <c r="B168" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="C168" s="25" t="s">
+        <v>23</v>
+      </c>
+      <c r="D168" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="E168" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="F168" s="23" t="s">
+        <v>6</v>
+      </c>
+      <c r="G168" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="H168" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="I168" s="25"/>
+      <c r="J168" s="25" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="169" spans="1:10" ht="17" x14ac:dyDescent="0.2">
@@ -5842,7 +5843,7 @@
         <v>55</v>
       </c>
       <c r="B169" s="13" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C169" s="11" t="s">
         <v>22</v>
@@ -5857,7 +5858,7 @@
         <v>5</v>
       </c>
       <c r="G169" s="14" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H169" s="14" t="s">
         <v>5</v>
@@ -5874,7 +5875,7 @@
         <v>55</v>
       </c>
       <c r="B170" s="13" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="C170" s="11" t="s">
         <v>22</v>
@@ -5889,7 +5890,7 @@
         <v>5</v>
       </c>
       <c r="G170" s="14" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H170" s="14" t="s">
         <v>5</v>
@@ -5906,7 +5907,7 @@
         <v>55</v>
       </c>
       <c r="B171" s="13" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="C171" s="11" t="s">
         <v>22</v>
@@ -5938,7 +5939,7 @@
         <v>55</v>
       </c>
       <c r="B172" s="13" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C172" s="11" t="s">
         <v>22</v>
@@ -5970,7 +5971,7 @@
         <v>55</v>
       </c>
       <c r="B173" s="13" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C173" s="11" t="s">
         <v>22</v>
@@ -6002,7 +6003,7 @@
         <v>55</v>
       </c>
       <c r="B174" s="13" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="C174" s="11" t="s">
         <v>22</v>
@@ -6017,7 +6018,7 @@
         <v>5</v>
       </c>
       <c r="G174" s="14" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H174" s="14" t="s">
         <v>5</v>
@@ -6030,62 +6031,64 @@
       </c>
     </row>
     <row r="175" spans="1:10" ht="17" x14ac:dyDescent="0.2">
-      <c r="A175" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="B175" s="23" t="s">
-        <v>15</v>
-      </c>
-      <c r="C175" s="23" t="s">
+      <c r="A175" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="B175" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="C175" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="D175" s="23" t="s">
-        <v>5</v>
-      </c>
-      <c r="E175" s="23" t="s">
-        <v>5</v>
-      </c>
-      <c r="F175" s="23" t="s">
-        <v>5</v>
-      </c>
-      <c r="G175" s="23" t="s">
-        <v>5</v>
-      </c>
-      <c r="H175" s="23" t="s">
-        <v>5</v>
-      </c>
-      <c r="I175" s="23"/>
-      <c r="J175" s="23" t="s">
-        <v>5</v>
+      <c r="D175" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="E175" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="F175" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="G175" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="H175" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="I175" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="J175" s="16" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="176" spans="1:10" ht="17" x14ac:dyDescent="0.2">
       <c r="A176" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="B176" s="25" t="s">
-        <v>39</v>
+      <c r="B176" s="23" t="s">
+        <v>15</v>
       </c>
       <c r="C176" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="D176" s="25" t="s">
-        <v>5</v>
-      </c>
-      <c r="E176" s="25" t="s">
-        <v>5</v>
-      </c>
-      <c r="F176" s="25" t="s">
-        <v>5</v>
-      </c>
-      <c r="G176" s="25" t="s">
+      <c r="D176" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="E176" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="F176" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="G176" s="23" t="s">
         <v>5</v>
       </c>
       <c r="H176" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="I176" s="25"/>
-      <c r="J176" s="25" t="s">
+      <c r="I176" s="23"/>
+      <c r="J176" s="23" t="s">
         <v>5</v>
       </c>
     </row>
@@ -6093,29 +6096,29 @@
       <c r="A177" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="B177" s="23" t="s">
-        <v>35</v>
+      <c r="B177" s="25" t="s">
+        <v>39</v>
       </c>
       <c r="C177" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="D177" s="23" t="s">
-        <v>5</v>
-      </c>
-      <c r="E177" s="23" t="s">
-        <v>5</v>
-      </c>
-      <c r="F177" s="23" t="s">
-        <v>5</v>
-      </c>
-      <c r="G177" s="23" t="s">
+      <c r="D177" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="E177" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="F177" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="G177" s="25" t="s">
         <v>5</v>
       </c>
       <c r="H177" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="I177" s="23"/>
-      <c r="J177" s="23" t="s">
+      <c r="I177" s="25"/>
+      <c r="J177" s="25" t="s">
         <v>5</v>
       </c>
     </row>
@@ -6123,29 +6126,29 @@
       <c r="A178" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="B178" s="25" t="s">
-        <v>21</v>
+      <c r="B178" s="23" t="s">
+        <v>35</v>
       </c>
       <c r="C178" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="D178" s="25" t="s">
-        <v>5</v>
-      </c>
-      <c r="E178" s="25" t="s">
-        <v>5</v>
-      </c>
-      <c r="F178" s="25" t="s">
-        <v>5</v>
-      </c>
-      <c r="G178" s="25" t="s">
+      <c r="D178" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="E178" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="F178" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="G178" s="23" t="s">
         <v>5</v>
       </c>
       <c r="H178" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="I178" s="25"/>
-      <c r="J178" s="25" t="s">
+      <c r="I178" s="23"/>
+      <c r="J178" s="23" t="s">
         <v>5</v>
       </c>
     </row>
@@ -6153,29 +6156,29 @@
       <c r="A179" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="B179" s="29" t="s">
-        <v>26</v>
+      <c r="B179" s="25" t="s">
+        <v>21</v>
       </c>
       <c r="C179" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="D179" s="23" t="s">
-        <v>5</v>
-      </c>
-      <c r="E179" s="23" t="s">
-        <v>5</v>
-      </c>
-      <c r="F179" s="23" t="s">
-        <v>5</v>
-      </c>
-      <c r="G179" s="23" t="s">
+      <c r="D179" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="E179" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="F179" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="G179" s="25" t="s">
         <v>5</v>
       </c>
       <c r="H179" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="I179" s="23"/>
-      <c r="J179" s="23" t="s">
+      <c r="I179" s="25"/>
+      <c r="J179" s="25" t="s">
         <v>5</v>
       </c>
     </row>
@@ -6183,29 +6186,29 @@
       <c r="A180" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="B180" s="25" t="s">
-        <v>13</v>
+      <c r="B180" s="29" t="s">
+        <v>26</v>
       </c>
       <c r="C180" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="D180" s="25" t="s">
-        <v>5</v>
-      </c>
-      <c r="E180" s="25" t="s">
-        <v>5</v>
-      </c>
-      <c r="F180" s="25" t="s">
-        <v>5</v>
-      </c>
-      <c r="G180" s="25" t="s">
+      <c r="D180" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="E180" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="F180" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="G180" s="23" t="s">
         <v>5</v>
       </c>
       <c r="H180" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="I180" s="25"/>
-      <c r="J180" s="25" t="s">
+      <c r="I180" s="23"/>
+      <c r="J180" s="23" t="s">
         <v>5</v>
       </c>
     </row>
@@ -6213,29 +6216,29 @@
       <c r="A181" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="B181" s="23" t="s">
-        <v>20</v>
+      <c r="B181" s="25" t="s">
+        <v>13</v>
       </c>
       <c r="C181" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="D181" s="23" t="s">
-        <v>5</v>
-      </c>
-      <c r="E181" s="23" t="s">
-        <v>5</v>
-      </c>
-      <c r="F181" s="23" t="s">
-        <v>5</v>
-      </c>
-      <c r="G181" s="23" t="s">
+      <c r="D181" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="E181" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="F181" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="G181" s="25" t="s">
         <v>5</v>
       </c>
       <c r="H181" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="I181" s="23"/>
-      <c r="J181" s="23" t="s">
+      <c r="I181" s="25"/>
+      <c r="J181" s="25" t="s">
         <v>5</v>
       </c>
     </row>
@@ -6243,29 +6246,29 @@
       <c r="A182" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="B182" s="28" t="s">
-        <v>37</v>
+      <c r="B182" s="23" t="s">
+        <v>20</v>
       </c>
       <c r="C182" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="D182" s="25" t="s">
-        <v>5</v>
-      </c>
-      <c r="E182" s="25" t="s">
-        <v>5</v>
-      </c>
-      <c r="F182" s="25" t="s">
-        <v>5</v>
-      </c>
-      <c r="G182" s="25" t="s">
+      <c r="D182" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="E182" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="F182" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="G182" s="23" t="s">
         <v>5</v>
       </c>
       <c r="H182" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="I182" s="25"/>
-      <c r="J182" s="25" t="s">
+      <c r="I182" s="23"/>
+      <c r="J182" s="23" t="s">
         <v>5</v>
       </c>
     </row>
@@ -6273,8 +6276,8 @@
       <c r="A183" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="B183" s="25" t="s">
-        <v>16</v>
+      <c r="B183" s="28" t="s">
+        <v>37</v>
       </c>
       <c r="C183" s="23" t="s">
         <v>22</v>
@@ -6303,29 +6306,29 @@
       <c r="A184" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="B184" s="23" t="s">
-        <v>19</v>
+      <c r="B184" s="25" t="s">
+        <v>16</v>
       </c>
       <c r="C184" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="D184" s="23" t="s">
-        <v>5</v>
-      </c>
-      <c r="E184" s="23" t="s">
-        <v>5</v>
-      </c>
-      <c r="F184" s="23" t="s">
-        <v>5</v>
-      </c>
-      <c r="G184" s="23" t="s">
+      <c r="D184" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="E184" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="F184" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="G184" s="25" t="s">
         <v>5</v>
       </c>
       <c r="H184" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="I184" s="23"/>
-      <c r="J184" s="23" t="s">
+      <c r="I184" s="25"/>
+      <c r="J184" s="25" t="s">
         <v>5</v>
       </c>
     </row>
@@ -6334,7 +6337,7 @@
         <v>46</v>
       </c>
       <c r="B185" s="23" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="C185" s="23" t="s">
         <v>22</v>
@@ -6359,140 +6362,138 @@
         <v>5</v>
       </c>
     </row>
-    <row r="186" spans="1:10" ht="34" x14ac:dyDescent="0.2">
-      <c r="A186" s="25" t="s">
-        <v>47</v>
-      </c>
-      <c r="B186" s="25" t="s">
-        <v>15</v>
+    <row r="186" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="A186" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="B186" s="23" t="s">
+        <v>14</v>
       </c>
       <c r="C186" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="D186" s="25" t="s">
-        <v>5</v>
-      </c>
-      <c r="E186" s="25" t="s">
-        <v>5</v>
-      </c>
-      <c r="F186" s="25" t="s">
-        <v>6</v>
-      </c>
-      <c r="G186" s="25" t="s">
-        <v>5</v>
-      </c>
-      <c r="H186" s="25" t="s">
-        <v>5</v>
-      </c>
-      <c r="I186" s="25" t="s">
-        <v>5</v>
-      </c>
-      <c r="J186" s="25" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="187" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="D186" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="E186" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="F186" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="G186" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="H186" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="I186" s="23"/>
+      <c r="J186" s="23" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="187" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A187" s="25" t="s">
         <v>47</v>
       </c>
-      <c r="B187" s="23" t="s">
-        <v>21</v>
+      <c r="B187" s="25" t="s">
+        <v>15</v>
       </c>
       <c r="C187" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="D187" s="23" t="s">
-        <v>5</v>
-      </c>
-      <c r="E187" s="23" t="s">
-        <v>5</v>
-      </c>
-      <c r="F187" s="23" t="s">
-        <v>5</v>
-      </c>
-      <c r="G187" s="23" t="s">
-        <v>5</v>
-      </c>
-      <c r="H187" s="23" t="s">
-        <v>5</v>
-      </c>
-      <c r="I187" s="23" t="s">
-        <v>5</v>
-      </c>
-      <c r="J187" s="23" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="188" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="D187" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="E187" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="F187" s="25" t="s">
+        <v>6</v>
+      </c>
+      <c r="G187" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="H187" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="I187" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="J187" s="25" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="188" spans="1:10" ht="17" x14ac:dyDescent="0.2">
       <c r="A188" s="25" t="s">
         <v>47</v>
       </c>
-      <c r="B188" s="25" t="s">
-        <v>14</v>
+      <c r="B188" s="23" t="s">
+        <v>21</v>
       </c>
       <c r="C188" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="D188" s="25" t="s">
-        <v>5</v>
-      </c>
-      <c r="E188" s="25" t="s">
-        <v>5</v>
-      </c>
-      <c r="F188" s="25" t="s">
-        <v>6</v>
-      </c>
-      <c r="G188" s="25" t="s">
-        <v>5</v>
-      </c>
-      <c r="H188" s="25" t="s">
-        <v>5</v>
-      </c>
-      <c r="I188" s="25" t="s">
-        <v>5</v>
-      </c>
-      <c r="J188" s="25" t="s">
+      <c r="D188" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="E188" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="F188" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="G188" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="H188" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="I188" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="J188" s="23" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="189" spans="1:10" ht="34" x14ac:dyDescent="0.2">
-      <c r="A189" s="23" t="s">
-        <v>48</v>
-      </c>
-      <c r="B189" s="23" t="s">
-        <v>15</v>
+      <c r="A189" s="25" t="s">
+        <v>47</v>
+      </c>
+      <c r="B189" s="25" t="s">
+        <v>14</v>
       </c>
       <c r="C189" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="D189" s="23" t="s">
-        <v>6</v>
-      </c>
-      <c r="E189" s="23" t="s">
-        <v>5</v>
-      </c>
-      <c r="F189" s="23" t="s">
-        <v>6</v>
-      </c>
-      <c r="G189" s="23" t="s">
-        <v>5</v>
-      </c>
-      <c r="H189" s="23" t="s">
-        <v>5</v>
-      </c>
-      <c r="I189" s="23" t="s">
-        <v>6</v>
-      </c>
-      <c r="J189" s="23" t="s">
-        <v>6</v>
+      <c r="D189" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="E189" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="F189" s="25" t="s">
+        <v>6</v>
+      </c>
+      <c r="G189" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="H189" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="I189" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="J189" s="25" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="190" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A190" s="23" t="s">
         <v>48</v>
       </c>
-      <c r="B190" s="25" t="s">
-        <v>21</v>
+      <c r="B190" s="23" t="s">
+        <v>15</v>
       </c>
       <c r="C190" s="23" t="s">
         <v>22</v>
@@ -6500,23 +6501,23 @@
       <c r="D190" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="E190" s="25" t="s">
-        <v>5</v>
-      </c>
-      <c r="F190" s="25" t="s">
-        <v>5</v>
-      </c>
-      <c r="G190" s="25" t="s">
-        <v>5</v>
-      </c>
-      <c r="H190" s="25" t="s">
-        <v>5</v>
-      </c>
-      <c r="I190" s="25" t="s">
-        <v>5</v>
-      </c>
-      <c r="J190" s="25" t="s">
-        <v>5</v>
+      <c r="E190" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="F190" s="23" t="s">
+        <v>6</v>
+      </c>
+      <c r="G190" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="H190" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="I190" s="23" t="s">
+        <v>6</v>
+      </c>
+      <c r="J190" s="23" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="191" spans="1:10" ht="34" x14ac:dyDescent="0.2">
@@ -6524,19 +6525,19 @@
         <v>48</v>
       </c>
       <c r="B191" s="25" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="C191" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="D191" s="25" t="s">
+      <c r="D191" s="23" t="s">
         <v>6</v>
       </c>
       <c r="E191" s="25" t="s">
         <v>5</v>
       </c>
       <c r="F191" s="25" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G191" s="25" t="s">
         <v>5</v>
@@ -6545,10 +6546,10 @@
         <v>5</v>
       </c>
       <c r="I191" s="25" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J191" s="25" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="192" spans="1:10" ht="34" x14ac:dyDescent="0.2">
@@ -6556,7 +6557,7 @@
         <v>48</v>
       </c>
       <c r="B192" s="25" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="C192" s="23" t="s">
         <v>22</v>
@@ -6568,7 +6569,7 @@
         <v>5</v>
       </c>
       <c r="F192" s="25" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G192" s="25" t="s">
         <v>5</v>
@@ -6587,31 +6588,31 @@
       <c r="A193" s="23" t="s">
         <v>48</v>
       </c>
-      <c r="B193" s="23" t="s">
-        <v>16</v>
+      <c r="B193" s="25" t="s">
+        <v>13</v>
       </c>
       <c r="C193" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="D193" s="23" t="s">
-        <v>6</v>
-      </c>
-      <c r="E193" s="23" t="s">
-        <v>5</v>
-      </c>
-      <c r="F193" s="23" t="s">
-        <v>6</v>
-      </c>
-      <c r="G193" s="23" t="s">
-        <v>5</v>
-      </c>
-      <c r="H193" s="23" t="s">
-        <v>5</v>
-      </c>
-      <c r="I193" s="23" t="s">
-        <v>6</v>
-      </c>
-      <c r="J193" s="23" t="s">
+      <c r="D193" s="25" t="s">
+        <v>6</v>
+      </c>
+      <c r="E193" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="F193" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="G193" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="H193" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="I193" s="25" t="s">
+        <v>6</v>
+      </c>
+      <c r="J193" s="25" t="s">
         <v>6</v>
       </c>
     </row>
@@ -6620,7 +6621,7 @@
         <v>48</v>
       </c>
       <c r="B194" s="23" t="s">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="C194" s="23" t="s">
         <v>22</v>
@@ -6641,7 +6642,7 @@
         <v>5</v>
       </c>
       <c r="I194" s="23" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J194" s="23" t="s">
         <v>6</v>
@@ -6651,31 +6652,31 @@
       <c r="A195" s="23" t="s">
         <v>48</v>
       </c>
-      <c r="B195" s="25" t="s">
-        <v>17</v>
+      <c r="B195" s="23" t="s">
+        <v>40</v>
       </c>
       <c r="C195" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="D195" s="25" t="s">
-        <v>6</v>
-      </c>
-      <c r="E195" s="25" t="s">
-        <v>5</v>
-      </c>
-      <c r="F195" s="25" t="s">
-        <v>6</v>
-      </c>
-      <c r="G195" s="25" t="s">
-        <v>5</v>
-      </c>
-      <c r="H195" s="25" t="s">
-        <v>5</v>
-      </c>
-      <c r="I195" s="25" t="s">
-        <v>5</v>
-      </c>
-      <c r="J195" s="25" t="s">
+      <c r="D195" s="23" t="s">
+        <v>6</v>
+      </c>
+      <c r="E195" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="F195" s="23" t="s">
+        <v>6</v>
+      </c>
+      <c r="G195" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="H195" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="I195" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="J195" s="23" t="s">
         <v>6</v>
       </c>
     </row>
@@ -6684,7 +6685,7 @@
         <v>48</v>
       </c>
       <c r="B196" s="25" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C196" s="23" t="s">
         <v>22</v>
@@ -6705,7 +6706,7 @@
         <v>5</v>
       </c>
       <c r="I196" s="25" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J196" s="25" t="s">
         <v>6</v>
@@ -6715,38 +6716,70 @@
       <c r="A197" s="23" t="s">
         <v>48</v>
       </c>
-      <c r="B197" s="23" t="s">
-        <v>14</v>
+      <c r="B197" s="25" t="s">
+        <v>19</v>
       </c>
       <c r="C197" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="D197" s="23" t="s">
-        <v>6</v>
-      </c>
-      <c r="E197" s="23" t="s">
-        <v>5</v>
-      </c>
-      <c r="F197" s="23" t="s">
-        <v>6</v>
-      </c>
-      <c r="G197" s="23" t="s">
-        <v>5</v>
-      </c>
-      <c r="H197" s="23" t="s">
-        <v>5</v>
-      </c>
-      <c r="I197" s="23" t="s">
-        <v>6</v>
-      </c>
-      <c r="J197" s="23" t="s">
+      <c r="D197" s="25" t="s">
+        <v>6</v>
+      </c>
+      <c r="E197" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="F197" s="25" t="s">
+        <v>6</v>
+      </c>
+      <c r="G197" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="H197" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="I197" s="25" t="s">
+        <v>6</v>
+      </c>
+      <c r="J197" s="25" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="198" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="A198" s="23" t="s">
+        <v>48</v>
+      </c>
+      <c r="B198" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="C198" s="23" t="s">
+        <v>22</v>
+      </c>
+      <c r="D198" s="23" t="s">
+        <v>6</v>
+      </c>
+      <c r="E198" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="F198" s="23" t="s">
+        <v>6</v>
+      </c>
+      <c r="G198" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="H198" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="I198" s="23" t="s">
+        <v>6</v>
+      </c>
+      <c r="J198" s="23" t="s">
         <v>6</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J197">
-    <sortCondition ref="A2:A197"/>
-    <sortCondition ref="B2:B197"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J198">
+    <sortCondition ref="A2:A198"/>
+    <sortCondition ref="B2:B198"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6754,15 +6787,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="66b5d41f-65e9-4808-95b5-49073c9d5630">
@@ -6771,6 +6795,15 @@
     <TaxCatchAll xmlns="f7f8f54e-e19b-4cd3-934a-81b57a2c13ba" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -6991,20 +7024,20 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2F5AED06-1D9E-4A9F-85B0-2D70E5AF734B}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B4EB8B42-1E5E-46D3-BE50-95104077392D}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="66b5d41f-65e9-4808-95b5-49073c9d5630"/>
     <ds:schemaRef ds:uri="f7f8f54e-e19b-4cd3-934a-81b57a2c13ba"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2F5AED06-1D9E-4A9F-85B0-2D70E5AF734B}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
